--- a/resources/tool_obs_latrine_iphra_v2.xlsx
+++ b/resources/tool_obs_latrine_iphra_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652A1347-7597-4B96-87E8-376AA87E536B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40582D92-ED9C-40C6-BD30-68C710EDC74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="1" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="372">
   <si>
     <t>type</t>
   </si>
@@ -1041,9 +1041,6 @@
     </r>
   </si>
   <si>
-    <t>dk</t>
-  </si>
-  <si>
     <t>Toilet superstructure (walls, doors, roof, platform, etc.) absent, incomplete, damaged</t>
   </si>
   <si>
@@ -1227,17 +1224,146 @@
     <t>indicator_code</t>
   </si>
   <si>
-    <t>57004, 57005</t>
-  </si>
-  <si>
     <t>containment_water</t>
+  </si>
+  <si>
+    <t>label::French (fr)</t>
+  </si>
+  <si>
+    <t>yes_no_dnk</t>
+  </si>
+  <si>
+    <t>Oui</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>Ne sait pas</t>
+  </si>
+  <si>
+    <t>yes_no_dnk_pnta</t>
+  </si>
+  <si>
+    <t>prefer_not_to_answer</t>
+  </si>
+  <si>
+    <t>Decline to answer</t>
+  </si>
+  <si>
+    <t>Préfère ne pas répondre</t>
+  </si>
+  <si>
+    <t>yes_no_other</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Autre</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>Homme</t>
+  </si>
+  <si>
+    <t>Femme</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>Team 1</t>
+  </si>
+  <si>
+    <t>Équipe 1</t>
+  </si>
+  <si>
+    <t>Team 2</t>
+  </si>
+  <si>
+    <t>Équipe 2</t>
+  </si>
+  <si>
+    <t>Team 3</t>
+  </si>
+  <si>
+    <t>Équipe 3</t>
+  </si>
+  <si>
+    <t>Team 4</t>
+  </si>
+  <si>
+    <t>Équipe 4</t>
+  </si>
+  <si>
+    <t>Team 5</t>
+  </si>
+  <si>
+    <t>Équipe 5</t>
+  </si>
+  <si>
+    <t>admin1</t>
+  </si>
+  <si>
+    <t>admin1a</t>
+  </si>
+  <si>
+    <t>To be updated by country</t>
+  </si>
+  <si>
+    <t>À mettre à jour par le pays</t>
+  </si>
+  <si>
+    <t>admin1b</t>
+  </si>
+  <si>
+    <t>admin1c</t>
+  </si>
+  <si>
+    <t>admin2</t>
+  </si>
+  <si>
+    <t>admin2a</t>
+  </si>
+  <si>
+    <t>admin2b</t>
+  </si>
+  <si>
+    <t>admin2c</t>
+  </si>
+  <si>
+    <t>admin3</t>
+  </si>
+  <si>
+    <t>admin3a</t>
+  </si>
+  <si>
+    <t>admin3b</t>
+  </si>
+  <si>
+    <t>admin3c</t>
+  </si>
+  <si>
+    <t>admin4</t>
+  </si>
+  <si>
+    <t>admin4a</t>
+  </si>
+  <si>
+    <t>admin4b</t>
+  </si>
+  <si>
+    <t>admin4c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1270,8 +1396,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1302,6 +1434,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1315,7 +1453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1338,11 +1476,66 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1762,7 +1955,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2017,8 +2210,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>57004</v>
+      <c r="A15" s="12">
+        <v>14902</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>52</v>
@@ -2034,8 +2227,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>57004</v>
+      <c r="A16" s="12">
+        <v>14902</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>26</v>
@@ -2054,8 +2247,8 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>57005</v>
+      <c r="A17" s="12">
+        <v>14804</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>210</v>
@@ -2071,8 +2264,8 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>57005</v>
+      <c r="A18" s="12">
+        <v>14804</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>26</v>
@@ -2091,8 +2284,8 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>328</v>
+      <c r="A19" s="12">
+        <v>14902</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>30</v>
@@ -2108,8 +2301,8 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>328</v>
+      <c r="A20" s="12">
+        <v>14902</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>54</v>
@@ -2128,8 +2321,8 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>57101</v>
+      <c r="A21" s="12">
+        <v>14903</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>30</v>
@@ -2145,8 +2338,8 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>57101</v>
+      <c r="A22" s="12">
+        <v>14903</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>30</v>
@@ -2165,8 +2358,8 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>57101</v>
+      <c r="A23" s="12">
+        <v>14903</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>91</v>
@@ -2185,8 +2378,8 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>57102</v>
+      <c r="A24" s="12">
+        <v>14904</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>204</v>
@@ -2202,8 +2395,8 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>57102</v>
+      <c r="A25" s="12">
+        <v>14904</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>30</v>
@@ -2222,8 +2415,8 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>57102</v>
+      <c r="A26" s="12">
+        <v>14904</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>30</v>
@@ -2242,14 +2435,14 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>57102</v>
+      <c r="A27" s="12">
+        <v>14904</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>193</v>
@@ -2262,8 +2455,8 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>57102</v>
+      <c r="A28" s="12">
+        <v>14904</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>30</v>
@@ -2282,8 +2475,8 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>57102</v>
+      <c r="A29" s="12">
+        <v>14904</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>30</v>
@@ -2302,8 +2495,8 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>57102</v>
+      <c r="A30" s="12">
+        <v>14904</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>30</v>
@@ -2322,8 +2515,8 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>57102</v>
+      <c r="A31" s="12">
+        <v>14904</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>30</v>
@@ -2339,8 +2532,8 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>57103</v>
+      <c r="A32" s="12">
+        <v>14905</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>102</v>
@@ -2359,8 +2552,8 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>57103</v>
+      <c r="A33" s="12">
+        <v>14905</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>26</v>
@@ -2379,8 +2572,8 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>57103</v>
+      <c r="A34" s="12">
+        <v>14905</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>122</v>
@@ -2396,8 +2589,8 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>57103</v>
+      <c r="A35" s="12">
+        <v>14905</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>26</v>
@@ -2416,8 +2609,8 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>57104</v>
+      <c r="A36" s="12">
+        <v>14906</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>30</v>
@@ -2433,8 +2626,8 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>57104</v>
+      <c r="A37" s="12">
+        <v>14906</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>190</v>
@@ -2456,8 +2649,8 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>57104</v>
+      <c r="A38" s="12">
+        <v>14906</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>26</v>
@@ -2476,8 +2669,8 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>57104</v>
+      <c r="A39" s="12">
+        <v>14907</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>30</v>
@@ -2493,11 +2686,11 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>57104</v>
+      <c r="A40" s="12">
+        <v>14907</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>239</v>
@@ -2516,14 +2709,14 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>57104</v>
+      <c r="A41" s="12">
+        <v>14907</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>63</v>
@@ -2532,12 +2725,12 @@
         <v>1</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>57105</v>
+      <c r="A42" s="12">
+        <v>14908</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>166</v>
@@ -2556,88 +2749,88 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>10000</v>
+      <c r="A43" s="12">
+        <v>14909</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>57106</v>
+      <c r="A44" s="12">
+        <v>14909</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>204</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>57106</v>
+      <c r="A45" s="12">
+        <v>14909</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F45" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="F46" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D45" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F45" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>57106</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="F46" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>272</v>
-      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>57106</v>
+      <c r="A47" s="12">
+        <v>14909</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>63</v>
@@ -2646,21 +2839,21 @@
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>57106</v>
+      <c r="A48" s="12">
+        <v>14909</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>245</v>
@@ -2669,29 +2862,29 @@
         <v>1</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>57106</v>
+      <c r="A49" s="12">
+        <v>14909</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F49" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>57106</v>
+      <c r="A50" s="12">
+        <v>14909</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>139</v>
@@ -2706,12 +2899,12 @@
         <v>1</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>20101</v>
+      <c r="A51" s="12">
+        <v>13307</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>156</v>
@@ -2727,11 +2920,14 @@
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <v>14910</v>
+      </c>
       <c r="B52" s="2" t="s">
         <v>204</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>264</v>
@@ -2747,8 +2943,8 @@
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>57107</v>
+      <c r="A53" s="12">
+        <v>14910</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>30</v>
@@ -2767,8 +2963,8 @@
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>57107</v>
+      <c r="A54" s="12">
+        <v>14910</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>30</v>
@@ -2787,8 +2983,8 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>57107</v>
+      <c r="A55" s="12">
+        <v>14910</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>30</v>
@@ -2807,8 +3003,8 @@
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>57107</v>
+      <c r="A56" s="12">
+        <v>14910</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>30</v>
@@ -2817,7 +3013,7 @@
         <v>262</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F56" s="2" t="b">
         <v>1</v>
@@ -2827,8 +3023,8 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>57108</v>
+      <c r="A57" s="12">
+        <v>14911</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>173</v>
@@ -2844,8 +3040,8 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>57108</v>
+      <c r="A58" s="12">
+        <v>14911</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>26</v>
@@ -2864,8 +3060,8 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>57108</v>
+      <c r="A59" s="12">
+        <v>14911</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>30</v>
@@ -2881,8 +3077,8 @@
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>57108</v>
+      <c r="A60" s="12">
+        <v>14911</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>54</v>
@@ -2901,14 +3097,14 @@
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>57108</v>
+      <c r="A61" s="12">
+        <v>14911</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>254</v>
@@ -2918,14 +3114,14 @@
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>57108</v>
+      <c r="A62" s="12">
+        <v>14911</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>255</v>
@@ -2934,43 +3130,43 @@
         <v>1</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>57006</v>
+      <c r="A63" s="12">
+        <v>14805</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>204</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>57006</v>
+      <c r="A64" s="12">
+        <v>14805</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F64" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>57006</v>
+      <c r="A65" s="12">
+        <v>14805</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>26</v>
@@ -2986,8 +3182,8 @@
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>57006</v>
+      <c r="A66" s="12">
+        <v>14805</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>30</v>
@@ -3030,10 +3226,10 @@
         <v>26</v>
       </c>
       <c r="C68" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D68" s="8" t="s">
         <v>325</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="145" spans="2:26" x14ac:dyDescent="0.25">
@@ -3078,13 +3274,13 @@
   </sheetData>
   <autoFilter ref="B1:M67" xr:uid="{6D2A72A4-B69F-42B0-BA64-020C51FE6931}"/>
   <conditionalFormatting sqref="C8:C9">
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:C67">
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -3093,7 +3289,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D63B81B-C0DE-4D5C-B8D8-1821B93262B2}">
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" style="2" customWidth="1"/>
@@ -3103,9 +3299,9 @@
     <col min="5" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>32</v>
@@ -3116,9 +3312,12 @@
       <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="E1" s="7" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="13">
         <v>10000</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -3131,8 +3330,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="13">
         <v>10000</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -3145,659 +3344,746 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13">
         <v>10000</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>57004</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="E6" s="14" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B7" t="s">
+        <v>333</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B8" t="s">
+        <v>333</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B9" t="s">
+        <v>333</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B10" t="s">
+        <v>333</v>
+      </c>
+      <c r="C10" t="s">
+        <v>334</v>
+      </c>
+      <c r="D10" t="s">
+        <v>335</v>
+      </c>
+      <c r="E10" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B11" t="s">
+        <v>337</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E13" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="C16" s="13">
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="C17" s="13">
+        <v>2</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="C18" s="13">
+        <v>3</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="C19" s="13">
+        <v>4</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="C20" s="13">
+        <v>5</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13">
+        <v>10000</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="12">
+        <v>14902</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>57004</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <v>14902</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J34" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>57004</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <v>14902</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>57004</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="12">
+        <v>14902</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>57004</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <v>14902</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>57004</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <v>14902</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>57004</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <v>14902</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>57101</v>
-      </c>
-      <c r="B12" s="3" t="s">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <v>14903</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>57101</v>
-      </c>
-      <c r="B13" s="3" t="s">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="12">
+        <v>14903</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>57101</v>
-      </c>
-      <c r="B14" s="3" t="s">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <v>14903</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>57103</v>
-      </c>
-      <c r="B15" s="3" t="s">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>57103</v>
-      </c>
-      <c r="B16" s="3" t="s">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>57103</v>
-      </c>
-      <c r="B17" s="3" t="s">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>57103</v>
-      </c>
-      <c r="B18" s="3" t="s">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>57103</v>
-      </c>
-      <c r="B19" s="3" t="s">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>57103</v>
-      </c>
-      <c r="B20" s="3" t="s">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>57103</v>
-      </c>
-      <c r="B21" s="3" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>57103</v>
-      </c>
-      <c r="B22" s="3" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>57103</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>57103</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>57103</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>57103</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>57103</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>57103</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>57103</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>57103</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>57103</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>57106</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>57106</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>57106</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>57106</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>57106</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>20101</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>20101</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>20101</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>20101</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>57105</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>57105</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>57105</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>57105</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>57108</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>57108</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>57108</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>57108</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>57108</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>57108</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>33</v>
@@ -3807,440 +4093,847 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>57104</v>
-      </c>
-      <c r="B51" s="2" t="s">
+      <c r="A51" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="12">
+        <v>14905</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="12">
+        <v>13307</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
+        <v>13307</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="12">
+        <v>13307</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="12">
+        <v>13307</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="12">
+        <v>14908</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
+        <v>14908</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="12">
+        <v>14908</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="12">
+        <v>14908</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="12">
+        <v>14911</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
+        <v>14911</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="12">
+        <v>14911</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="12">
+        <v>14911</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="12">
+        <v>14911</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="12">
+        <v>14911</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="12">
+        <v>14906</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C79" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D79" s="8" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>57104</v>
-      </c>
-      <c r="B52" s="2" t="s">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="12">
+        <v>14906</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C80" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D80" s="8" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>57104</v>
-      </c>
-      <c r="B53" s="2" t="s">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="12">
+        <v>14906</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C81" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="D53" s="8" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>57104</v>
-      </c>
-      <c r="B54" s="2" t="s">
+      <c r="D81" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="12">
+        <v>14906</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C82" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D82" s="8" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>57104</v>
-      </c>
-      <c r="B55" s="2" t="s">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
+        <v>14906</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C83" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D83" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>57005</v>
-      </c>
-      <c r="B56" s="2" t="s">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="12">
+        <v>14804</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C84" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D84" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>57005</v>
-      </c>
-      <c r="B57" s="2" t="s">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="12">
+        <v>14804</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C85" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
-        <v>57005</v>
-      </c>
-      <c r="B58" s="2" t="s">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="12">
+        <v>14804</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C86" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D86" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
-        <v>57005</v>
-      </c>
-      <c r="B59" s="2" t="s">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="12">
+        <v>14804</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C87" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D87" s="2" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>57005</v>
-      </c>
-      <c r="B60" s="2" t="s">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="12">
+        <v>14804</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>57005</v>
-      </c>
-      <c r="B61" s="2" t="s">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="12">
+        <v>14804</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D89" s="2" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
-        <v>57005</v>
-      </c>
-      <c r="B62" s="2" t="s">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="12">
+        <v>14804</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C90" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D90" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>57104</v>
-      </c>
-      <c r="B63" s="2" t="s">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="12">
+        <v>14907</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C91" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D91" s="8" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>57104</v>
-      </c>
-      <c r="B64" s="2" t="s">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="12">
+        <v>14907</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C92" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D92" s="8" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>57104</v>
-      </c>
-      <c r="B65" s="2" t="s">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="12">
+        <v>14907</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C93" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="D93" s="8" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>57104</v>
-      </c>
-      <c r="B66" s="2" t="s">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="12">
+        <v>14907</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C94" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="D94" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="D66" s="8" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>57104</v>
-      </c>
-      <c r="B67" s="2" t="s">
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="12">
+        <v>14907</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C95" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D95" s="8" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>57106</v>
-      </c>
-      <c r="B68" s="2" t="s">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D96" t="s">
         <v>274</v>
       </c>
-      <c r="C68" s="2" t="s">
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D97" s="2" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>57106</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C69" s="2" t="s">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D98" s="2" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>57106</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C70" s="2" t="s">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D99" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>57106</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C71" s="2" t="s">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D100" s="2" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>57106</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C72" s="2" t="s">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>57106</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C73" s="2" t="s">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D102" s="2" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>57106</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>57106</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C75" s="2" t="s">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D103" s="2" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>57106</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C76" s="2" t="s">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D104" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>57106</v>
-      </c>
-      <c r="B77" s="2" t="s">
+    <row r="105" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D105" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="C77" s="2" t="s">
+    </row>
+    <row r="106" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="D106" s="10" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>57106</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D78" s="10" t="s">
+    <row r="107" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D107" s="10" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>57106</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>57106</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C80" s="2" t="s">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D108" s="2" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>57106</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C81" s="2" t="s">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="12">
+        <v>14909</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D109" s="2" t="s">
         <v>197</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C4:C6">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C10">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C12">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:C20">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:C32">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4281,6 +4974,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
     <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
@@ -4521,41 +5234,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0D1DE91-ED80-491A-8D54-5B9834655099}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08C12AF5-9188-465E-96FA-F5C863409212}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
-    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4574,9 +5256,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08C12AF5-9188-465E-96FA-F5C863409212}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0D1DE91-ED80-491A-8D54-5B9834655099}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>